--- a/output/yearly_total_coral_cover_iteration_49_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_49_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.278074931577749</v>
+        <v>1.261885911934719</v>
       </c>
       <c r="C3" t="n">
-        <v>4.643064720804872</v>
+        <v>4.601909857042846</v>
       </c>
       <c r="D3" t="n">
-        <v>6.01752938108356</v>
+        <v>6.048562426014803</v>
       </c>
       <c r="E3" t="n">
-        <v>11.93866903346618</v>
+        <v>11.91235819499237</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.439652863458847</v>
+        <v>1.394212289525907</v>
       </c>
       <c r="C4" t="n">
-        <v>5.151038156950941</v>
+        <v>5.036747155997938</v>
       </c>
       <c r="D4" t="n">
-        <v>6.258088182043286</v>
+        <v>6.307863323271734</v>
       </c>
       <c r="E4" t="n">
-        <v>12.84877920245307</v>
+        <v>12.73882276879558</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.657015199494587</v>
+        <v>1.57221837420099</v>
       </c>
       <c r="C5" t="n">
-        <v>5.784087157845717</v>
+        <v>5.556536449297267</v>
       </c>
       <c r="D5" t="n">
-        <v>6.57264779396236</v>
+        <v>6.544771669972977</v>
       </c>
       <c r="E5" t="n">
-        <v>14.01375015130266</v>
+        <v>13.67352649347123</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.906106359788291</v>
+        <v>1.789344558922046</v>
       </c>
       <c r="C6" t="n">
-        <v>6.582186750758218</v>
+        <v>6.195068097932655</v>
       </c>
       <c r="D6" t="n">
-        <v>6.888697051857965</v>
+        <v>6.934161024121583</v>
       </c>
       <c r="E6" t="n">
-        <v>15.37699016240447</v>
+        <v>14.91857368097628</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.195566948461135</v>
+        <v>2.038104034931386</v>
       </c>
       <c r="C7" t="n">
-        <v>7.520368792120061</v>
+        <v>6.918245360538206</v>
       </c>
       <c r="D7" t="n">
-        <v>7.247878606245766</v>
+        <v>7.315546583414681</v>
       </c>
       <c r="E7" t="n">
-        <v>16.96381434682696</v>
+        <v>16.27189597888427</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.416796407663053</v>
+        <v>1.275582688116245</v>
       </c>
       <c r="C8" t="n">
-        <v>5.205923710498516</v>
+        <v>4.586332222002944</v>
       </c>
       <c r="D8" t="n">
-        <v>5.4529558585542</v>
+        <v>5.525701561743669</v>
       </c>
       <c r="E8" t="n">
-        <v>12.07567597671577</v>
+        <v>11.38761647186286</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.812025097588897</v>
+        <v>1.619886089420336</v>
       </c>
       <c r="C9" t="n">
-        <v>6.470394713592489</v>
+        <v>5.601801574999392</v>
       </c>
       <c r="D9" t="n">
-        <v>5.893191585622378</v>
+        <v>5.953435514144368</v>
       </c>
       <c r="E9" t="n">
-        <v>14.17561139680376</v>
+        <v>13.1751231785641</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.236009533330929</v>
+        <v>1.995738919697611</v>
       </c>
       <c r="C10" t="n">
-        <v>7.914380561291614</v>
+        <v>6.814544751706456</v>
       </c>
       <c r="D10" t="n">
-        <v>6.33181186806341</v>
+        <v>6.444940975527816</v>
       </c>
       <c r="E10" t="n">
-        <v>16.48220196268595</v>
+        <v>15.25522464693188</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.657671464217784</v>
+        <v>2.398864741989623</v>
       </c>
       <c r="C11" t="n">
-        <v>9.480483140374602</v>
+        <v>8.130681844165126</v>
       </c>
       <c r="D11" t="n">
-        <v>6.828005866413088</v>
+        <v>6.906203879567402</v>
       </c>
       <c r="E11" t="n">
-        <v>18.96616047100547</v>
+        <v>17.43575046572215</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.068222243874422</v>
+        <v>2.82453412483583</v>
       </c>
       <c r="C12" t="n">
-        <v>11.08621880496141</v>
+        <v>9.554873189838215</v>
       </c>
       <c r="D12" t="n">
-        <v>7.283016208155885</v>
+        <v>7.396480864841888</v>
       </c>
       <c r="E12" t="n">
-        <v>21.43745725699172</v>
+        <v>19.77588817951593</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.45320420487579</v>
+        <v>3.243901953396646</v>
       </c>
       <c r="C13" t="n">
-        <v>12.68676432990874</v>
+        <v>11.04003615205641</v>
       </c>
       <c r="D13" t="n">
-        <v>7.663848288546814</v>
+        <v>7.903391200252862</v>
       </c>
       <c r="E13" t="n">
-        <v>23.80381682333135</v>
+        <v>22.18732930570592</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.974441895395972</v>
+        <v>1.873920747958142</v>
       </c>
       <c r="C14" t="n">
-        <v>8.793170575242193</v>
+        <v>7.749592400581919</v>
       </c>
       <c r="D14" t="n">
-        <v>5.833171794506933</v>
+        <v>6.018407951344222</v>
       </c>
       <c r="E14" t="n">
-        <v>16.6007842651451</v>
+        <v>15.64192109988428</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2.027201017022196</v>
+        <v>1.963269606521644</v>
       </c>
       <c r="C15" t="n">
-        <v>9.482298558761199</v>
+        <v>8.402012837439138</v>
       </c>
       <c r="D15" t="n">
-        <v>5.800980287284681</v>
+        <v>6.030846694757028</v>
       </c>
       <c r="E15" t="n">
-        <v>17.31047986306807</v>
+        <v>16.39612913871781</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.367955827689222</v>
+        <v>2.313625909736204</v>
       </c>
       <c r="C16" t="n">
-        <v>11.2003766761472</v>
+        <v>9.977462648352164</v>
       </c>
       <c r="D16" t="n">
-        <v>6.251327594176778</v>
+        <v>6.572094021585338</v>
       </c>
       <c r="E16" t="n">
-        <v>19.8196600980132</v>
+        <v>18.8631825796737</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.909666181869768</v>
+        <v>1.875442456899725</v>
       </c>
       <c r="C17" t="n">
-        <v>10.3126018621509</v>
+        <v>9.279832729714382</v>
       </c>
       <c r="D17" t="n">
-        <v>5.773589526336194</v>
+        <v>6.131230397516265</v>
       </c>
       <c r="E17" t="n">
-        <v>17.99585757035686</v>
+        <v>17.28650558413037</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.199556643979767</v>
+        <v>2.165234744239298</v>
       </c>
       <c r="C18" t="n">
-        <v>12.03127884563649</v>
+        <v>10.84007526868862</v>
       </c>
       <c r="D18" t="n">
-        <v>6.128314606834652</v>
+        <v>6.543446623575417</v>
       </c>
       <c r="E18" t="n">
-        <v>20.35915009645091</v>
+        <v>19.54875663650334</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.220919474024177</v>
+        <v>2.198005482607057</v>
       </c>
       <c r="C19" t="n">
-        <v>12.87745700940386</v>
+        <v>11.59794522645899</v>
       </c>
       <c r="D19" t="n">
-        <v>6.201189738920892</v>
+        <v>6.643035110694212</v>
       </c>
       <c r="E19" t="n">
-        <v>21.29956622234893</v>
+        <v>20.43898581976026</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.487316713571549</v>
+        <v>2.484450010275149</v>
       </c>
       <c r="C20" t="n">
-        <v>14.8506422677384</v>
+        <v>13.36036888764582</v>
       </c>
       <c r="D20" t="n">
-        <v>6.630419652694641</v>
+        <v>7.081964691785919</v>
       </c>
       <c r="E20" t="n">
-        <v>23.96837863400459</v>
+        <v>22.92678358970689</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.48604204748727</v>
+        <v>1.494062926230966</v>
       </c>
       <c r="C21" t="n">
-        <v>10.93726829140906</v>
+        <v>9.840233954252545</v>
       </c>
       <c r="D21" t="n">
-        <v>5.526120382526701</v>
+        <v>5.901550522107724</v>
       </c>
       <c r="E21" t="n">
-        <v>17.94943072142303</v>
+        <v>17.23584740259124</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_49_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_49_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.261885911934719</v>
+        <v>1.244931129082377</v>
       </c>
       <c r="C3" t="n">
-        <v>4.601909857042846</v>
+        <v>4.577660688747948</v>
       </c>
       <c r="D3" t="n">
-        <v>6.048562426014803</v>
+        <v>6.120897596863707</v>
       </c>
       <c r="E3" t="n">
-        <v>11.91235819499237</v>
+        <v>11.94348941469403</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.394212289525907</v>
+        <v>1.349419603076187</v>
       </c>
       <c r="C4" t="n">
-        <v>5.036747155997938</v>
+        <v>4.98273280855339</v>
       </c>
       <c r="D4" t="n">
-        <v>6.307863323271734</v>
+        <v>6.447064700117832</v>
       </c>
       <c r="E4" t="n">
-        <v>12.73882276879558</v>
+        <v>12.77921711174741</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.57221837420099</v>
+        <v>1.493389808709125</v>
       </c>
       <c r="C5" t="n">
-        <v>5.556536449297267</v>
+        <v>5.468200007619019</v>
       </c>
       <c r="D5" t="n">
-        <v>6.544771669972977</v>
+        <v>6.75546162692982</v>
       </c>
       <c r="E5" t="n">
-        <v>13.67352649347123</v>
+        <v>13.71705144325796</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.789344558922046</v>
+        <v>1.667397703326907</v>
       </c>
       <c r="C6" t="n">
-        <v>6.195068097932655</v>
+        <v>6.083446636066593</v>
       </c>
       <c r="D6" t="n">
-        <v>6.934161024121583</v>
+        <v>7.225821367114849</v>
       </c>
       <c r="E6" t="n">
-        <v>14.91857368097628</v>
+        <v>14.97666570650835</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.038104034931386</v>
+        <v>1.86426799632885</v>
       </c>
       <c r="C7" t="n">
-        <v>6.918245360538206</v>
+        <v>6.826532963828672</v>
       </c>
       <c r="D7" t="n">
-        <v>7.315546583414681</v>
+        <v>7.629799653394567</v>
       </c>
       <c r="E7" t="n">
-        <v>16.27189597888427</v>
+        <v>16.32060061355209</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.275582688116245</v>
+        <v>1.126417382368968</v>
       </c>
       <c r="C8" t="n">
-        <v>4.586332222002944</v>
+        <v>4.606854615686508</v>
       </c>
       <c r="D8" t="n">
-        <v>5.525701561743669</v>
+        <v>5.879981027363682</v>
       </c>
       <c r="E8" t="n">
-        <v>11.38761647186286</v>
+        <v>11.61325302541916</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.619886089420336</v>
+        <v>1.417370717380801</v>
       </c>
       <c r="C9" t="n">
-        <v>5.601801574999392</v>
+        <v>5.751635977530346</v>
       </c>
       <c r="D9" t="n">
-        <v>5.953435514144368</v>
+        <v>6.425945376803272</v>
       </c>
       <c r="E9" t="n">
-        <v>13.1751231785641</v>
+        <v>13.59495207171442</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.995738919697611</v>
+        <v>1.734624200648484</v>
       </c>
       <c r="C10" t="n">
-        <v>6.814544751706456</v>
+        <v>7.136536891267522</v>
       </c>
       <c r="D10" t="n">
-        <v>6.444940975527816</v>
+        <v>6.961419525627376</v>
       </c>
       <c r="E10" t="n">
-        <v>15.25522464693188</v>
+        <v>15.83258061754338</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.398864741989623</v>
+        <v>2.057108350383517</v>
       </c>
       <c r="C11" t="n">
-        <v>8.130681844165126</v>
+        <v>8.679029637124303</v>
       </c>
       <c r="D11" t="n">
-        <v>6.906203879567402</v>
+        <v>7.581531948852748</v>
       </c>
       <c r="E11" t="n">
-        <v>17.43575046572215</v>
+        <v>18.31766993636057</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.82453412483583</v>
+        <v>2.377098599355924</v>
       </c>
       <c r="C12" t="n">
-        <v>9.554873189838215</v>
+        <v>10.30188259820805</v>
       </c>
       <c r="D12" t="n">
-        <v>7.396480864841888</v>
+        <v>8.093271286344285</v>
       </c>
       <c r="E12" t="n">
-        <v>19.77588817951593</v>
+        <v>20.77225248390826</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.243901953396646</v>
+        <v>2.683300113445542</v>
       </c>
       <c r="C13" t="n">
-        <v>11.04003615205641</v>
+        <v>11.96008125148552</v>
       </c>
       <c r="D13" t="n">
-        <v>7.903391200252862</v>
+        <v>8.593077823127686</v>
       </c>
       <c r="E13" t="n">
-        <v>22.18732930570592</v>
+        <v>23.23645918805875</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.873920747958142</v>
+        <v>1.543042319195839</v>
       </c>
       <c r="C14" t="n">
-        <v>7.749592400581919</v>
+        <v>8.249527784015523</v>
       </c>
       <c r="D14" t="n">
-        <v>6.018407951344222</v>
+        <v>6.490903486444126</v>
       </c>
       <c r="E14" t="n">
-        <v>15.64192109988428</v>
+        <v>16.28347358965549</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.963269606521644</v>
+        <v>1.581772266128376</v>
       </c>
       <c r="C15" t="n">
-        <v>8.402012837439138</v>
+        <v>9.041091322995642</v>
       </c>
       <c r="D15" t="n">
-        <v>6.030846694757028</v>
+        <v>6.536338770196669</v>
       </c>
       <c r="E15" t="n">
-        <v>16.39612913871781</v>
+        <v>17.15920235932069</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.313625909736204</v>
+        <v>1.834081426119806</v>
       </c>
       <c r="C16" t="n">
-        <v>9.977462648352164</v>
+        <v>10.72117580422729</v>
       </c>
       <c r="D16" t="n">
-        <v>6.572094021585338</v>
+        <v>6.977516553531101</v>
       </c>
       <c r="E16" t="n">
-        <v>18.8631825796737</v>
+        <v>19.5327737838782</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.875442456899725</v>
+        <v>1.47132564940061</v>
       </c>
       <c r="C17" t="n">
-        <v>9.279832729714382</v>
+        <v>9.980152637061801</v>
       </c>
       <c r="D17" t="n">
-        <v>6.131230397516265</v>
+        <v>6.465819832600621</v>
       </c>
       <c r="E17" t="n">
-        <v>17.28650558413037</v>
+        <v>17.91729811906303</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.165234744239298</v>
+        <v>1.674419796978148</v>
       </c>
       <c r="C18" t="n">
-        <v>10.84007526868862</v>
+        <v>11.65721333536437</v>
       </c>
       <c r="D18" t="n">
-        <v>6.543446623575417</v>
+        <v>6.934643631286643</v>
       </c>
       <c r="E18" t="n">
-        <v>19.54875663650334</v>
+        <v>20.26627676362916</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.198005482607057</v>
+        <v>1.673771843493345</v>
       </c>
       <c r="C19" t="n">
-        <v>11.59794522645899</v>
+        <v>12.48378599747793</v>
       </c>
       <c r="D19" t="n">
-        <v>6.643035110694212</v>
+        <v>7.047259910440794</v>
       </c>
       <c r="E19" t="n">
-        <v>20.43898581976026</v>
+        <v>21.20481775141207</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.484450010275149</v>
+        <v>1.859371246981204</v>
       </c>
       <c r="C20" t="n">
-        <v>13.36036888764582</v>
+        <v>14.30805976403231</v>
       </c>
       <c r="D20" t="n">
-        <v>7.081964691785919</v>
+        <v>7.450620772207639</v>
       </c>
       <c r="E20" t="n">
-        <v>22.92678358970689</v>
+        <v>23.61805178322115</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.494062926230966</v>
+        <v>1.104024380810751</v>
       </c>
       <c r="C21" t="n">
-        <v>9.840233954252545</v>
+        <v>10.41775685875278</v>
       </c>
       <c r="D21" t="n">
-        <v>5.901550522107724</v>
+        <v>6.201837692405696</v>
       </c>
       <c r="E21" t="n">
-        <v>17.23584740259124</v>
+        <v>17.72361893196922</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_49_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_49_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.244931129082377</v>
+        <v>2.589054750046175</v>
       </c>
       <c r="C3" t="n">
-        <v>4.577660688747948</v>
+        <v>7.653702271664639</v>
       </c>
       <c r="D3" t="n">
-        <v>6.120897596863707</v>
+        <v>8.173017990480991</v>
       </c>
       <c r="E3" t="n">
-        <v>11.94348941469403</v>
+        <v>18.4157750121918</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.349419603076187</v>
+        <v>1.089130557834709</v>
       </c>
       <c r="C4" t="n">
-        <v>4.98273280855339</v>
+        <v>4.350269002450089</v>
       </c>
       <c r="D4" t="n">
-        <v>6.447064700117832</v>
+        <v>5.832151384039479</v>
       </c>
       <c r="E4" t="n">
-        <v>12.77921711174741</v>
+        <v>11.27155094432428</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.493389808709125</v>
+        <v>1.208018560101659</v>
       </c>
       <c r="C5" t="n">
-        <v>5.468200007619019</v>
+        <v>4.847232565218048</v>
       </c>
       <c r="D5" t="n">
-        <v>6.75546162692982</v>
+        <v>6.17753453967522</v>
       </c>
       <c r="E5" t="n">
-        <v>13.71705144325796</v>
+        <v>12.23278566499493</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.667397703326907</v>
+        <v>1.340824174430129</v>
       </c>
       <c r="C6" t="n">
-        <v>6.083446636066593</v>
+        <v>5.489248264871536</v>
       </c>
       <c r="D6" t="n">
-        <v>7.225821367114849</v>
+        <v>6.53328754564181</v>
       </c>
       <c r="E6" t="n">
-        <v>14.97666570650835</v>
+        <v>13.36335998494348</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.86426799632885</v>
+        <v>1.480226134352143</v>
       </c>
       <c r="C7" t="n">
-        <v>6.826532963828672</v>
+        <v>6.319220364059668</v>
       </c>
       <c r="D7" t="n">
-        <v>7.629799653394567</v>
+        <v>6.924377332165239</v>
       </c>
       <c r="E7" t="n">
-        <v>16.32060061355209</v>
+        <v>14.72382383057705</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.126417382368968</v>
+        <v>1.615547780951513</v>
       </c>
       <c r="C8" t="n">
-        <v>4.606854615686508</v>
+        <v>7.313392557535031</v>
       </c>
       <c r="D8" t="n">
-        <v>5.879981027363682</v>
+        <v>7.421107830297981</v>
       </c>
       <c r="E8" t="n">
-        <v>11.61325302541916</v>
+        <v>16.35004816878453</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.417370717380801</v>
+        <v>1.754458025377889</v>
       </c>
       <c r="C9" t="n">
-        <v>5.751635977530346</v>
+        <v>8.454743401835506</v>
       </c>
       <c r="D9" t="n">
-        <v>6.425945376803272</v>
+        <v>7.857603236738155</v>
       </c>
       <c r="E9" t="n">
-        <v>13.59495207171442</v>
+        <v>18.06680466395155</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.734624200648484</v>
+        <v>1.086107485208246</v>
       </c>
       <c r="C10" t="n">
-        <v>7.136536891267522</v>
+        <v>6.376971665366284</v>
       </c>
       <c r="D10" t="n">
-        <v>6.961419525627376</v>
+        <v>6.201729700158229</v>
       </c>
       <c r="E10" t="n">
-        <v>15.83258061754338</v>
+        <v>13.66480885073276</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.057108350383517</v>
+        <v>1.019780610309332</v>
       </c>
       <c r="C11" t="n">
-        <v>8.679029637124303</v>
+        <v>6.75320683806479</v>
       </c>
       <c r="D11" t="n">
-        <v>7.581531948852748</v>
+        <v>6.092205926272454</v>
       </c>
       <c r="E11" t="n">
-        <v>18.31766993636057</v>
+        <v>13.86519337464658</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.377098599355924</v>
+        <v>1.107823744426186</v>
       </c>
       <c r="C12" t="n">
-        <v>10.30188259820805</v>
+        <v>7.991573574724673</v>
       </c>
       <c r="D12" t="n">
-        <v>8.093271286344285</v>
+        <v>6.529594163468494</v>
       </c>
       <c r="E12" t="n">
-        <v>20.77225248390826</v>
+        <v>15.62899148261935</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.683300113445542</v>
+        <v>0.8832685920338128</v>
       </c>
       <c r="C13" t="n">
-        <v>11.96008125148552</v>
+        <v>7.63642634271339</v>
       </c>
       <c r="D13" t="n">
-        <v>8.593077823127686</v>
+        <v>5.997693074784614</v>
       </c>
       <c r="E13" t="n">
-        <v>23.23645918805875</v>
+        <v>14.51738800953182</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.543042319195839</v>
+        <v>0.9659121137773095</v>
       </c>
       <c r="C14" t="n">
-        <v>8.249527784015523</v>
+        <v>8.936162128365742</v>
       </c>
       <c r="D14" t="n">
-        <v>6.490903486444126</v>
+        <v>6.454205757259381</v>
       </c>
       <c r="E14" t="n">
-        <v>16.28347358965549</v>
+        <v>16.35627999940243</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.581772266128376</v>
+        <v>0.9420949144722819</v>
       </c>
       <c r="C15" t="n">
-        <v>9.041091322995642</v>
+        <v>9.657569976400383</v>
       </c>
       <c r="D15" t="n">
-        <v>6.536338770196669</v>
+        <v>6.551359510071645</v>
       </c>
       <c r="E15" t="n">
-        <v>17.15920235932069</v>
+        <v>17.15102440094431</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.834081426119806</v>
+        <v>1.044550104887479</v>
       </c>
       <c r="C16" t="n">
-        <v>10.72117580422729</v>
+        <v>11.27530366093532</v>
       </c>
       <c r="D16" t="n">
-        <v>6.977516553531101</v>
+        <v>7.034448102900374</v>
       </c>
       <c r="E16" t="n">
-        <v>19.5327737838782</v>
+        <v>19.35430186872317</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.47132564940061</v>
+        <v>0.6367222910663114</v>
       </c>
       <c r="C17" t="n">
-        <v>9.980152637061801</v>
+        <v>8.452494304391509</v>
       </c>
       <c r="D17" t="n">
-        <v>6.465819832600621</v>
+        <v>5.880825828071074</v>
       </c>
       <c r="E17" t="n">
-        <v>17.91729811906303</v>
+        <v>14.97004242352889</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.674419796978148</v>
+        <v>0.5124428491857077</v>
       </c>
       <c r="C18" t="n">
-        <v>11.65721333536437</v>
+        <v>7.465494249926979</v>
       </c>
       <c r="D18" t="n">
-        <v>6.934643631286643</v>
+        <v>5.389490554526672</v>
       </c>
       <c r="E18" t="n">
-        <v>20.26627676362916</v>
+        <v>13.36742765363936</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.673771843493345</v>
+        <v>0.6075545667731387</v>
       </c>
       <c r="C19" t="n">
-        <v>12.48378599747793</v>
+        <v>9.222920815299192</v>
       </c>
       <c r="D19" t="n">
-        <v>7.047259910440794</v>
+        <v>5.947162520447031</v>
       </c>
       <c r="E19" t="n">
-        <v>21.20481775141207</v>
+        <v>15.77763790251936</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.859371246981204</v>
+        <v>0.6970506874922779</v>
       </c>
       <c r="C20" t="n">
-        <v>14.30805976403231</v>
+        <v>11.04846103639205</v>
       </c>
       <c r="D20" t="n">
-        <v>7.450620772207639</v>
+        <v>6.590973029938004</v>
       </c>
       <c r="E20" t="n">
-        <v>23.61805178322115</v>
+        <v>18.33648475382233</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.104024380810751</v>
+        <v>0.7785553818988481</v>
       </c>
       <c r="C21" t="n">
-        <v>10.41775685875278</v>
+        <v>12.90639893172506</v>
       </c>
       <c r="D21" t="n">
-        <v>6.201837692405696</v>
+        <v>7.172236393191413</v>
       </c>
       <c r="E21" t="n">
-        <v>17.72361893196922</v>
+        <v>20.85719070681532</v>
       </c>
     </row>
   </sheetData>
